--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Test ValueSet for predicted susceptibility: LOINC codes for the expected efficacy of an antimicrobial substance derived from the genotype.</t>
+    <t>Test ValueSet for predicted susceptibility: LOINC codes for the predicted efficacy of an antimicrobial substance derived from the genotype.</t>
   </si>
   <si>
     <t>Purpose</t>
